--- a/Evo-M1_candidates_ReadMe_rows_2026-09-30.xlsx
+++ b/Evo-M1_candidates_ReadMe_rows_2026-09-30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_71F815DFE9B39ABCBECD963E2C549E60974E1F77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABDCAAC0-8C49-9044-87B6-D775C4E269A2}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_71F815DFE9B39ABCBECD963E2C549E60974E1F77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AAD6D03-96D4-014E-88AA-BA93C3686839}"/>
   <bookViews>
-    <workbookView xWindow="44000" yWindow="-4140" windowWidth="30460" windowHeight="13880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41140" yWindow="-5860" windowWidth="32840" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1_paste" sheetId="1" r:id="rId1"/>
@@ -4137,12 +4137,11 @@
   <dimension ref="A1:AG70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="81.83203125" customWidth="1"/>
+    <col min="1" max="1" width="132.83203125" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="5" max="12" width="3.33203125" customWidth="1"/>
     <col min="13" max="13" width="71.6640625" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="60" customWidth="1"/>
@@ -4265,7 +4264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -4338,7 +4337,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -4482,7 +4481,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>77</v>
       </c>
@@ -4553,7 +4552,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>90</v>
       </c>
@@ -4624,7 +4623,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>104</v>
       </c>
@@ -4697,7 +4696,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>118</v>
       </c>
@@ -4770,7 +4769,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>132</v>
       </c>
@@ -4841,7 +4840,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>157</v>
       </c>
@@ -5060,7 +5059,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>183</v>
       </c>
@@ -5206,7 +5205,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>203</v>
       </c>
@@ -5277,7 +5276,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>214</v>
       </c>
@@ -5352,7 +5351,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>228</v>
       </c>
@@ -5427,7 +5426,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -5504,7 +5503,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>246</v>
       </c>
@@ -5577,7 +5576,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>256</v>
       </c>
@@ -5650,7 +5649,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>268</v>
       </c>
@@ -5796,7 +5795,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>293</v>
       </c>
@@ -5869,7 +5868,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>307</v>
       </c>
@@ -5944,7 +5943,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="25" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>316</v>
       </c>
@@ -6015,7 +6014,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="26" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>326</v>
       </c>
@@ -6086,7 +6085,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="27" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>335</v>
       </c>
@@ -6159,7 +6158,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="28" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>344</v>
       </c>
@@ -6232,7 +6231,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="29" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>357</v>
       </c>
@@ -6305,7 +6304,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>374</v>
       </c>
@@ -6382,7 +6381,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="31" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>389</v>
       </c>
@@ -6455,7 +6454,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="32" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>401</v>
       </c>
@@ -6599,7 +6598,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>417</v>
       </c>
@@ -6670,7 +6669,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>428</v>
       </c>
@@ -6741,7 +6740,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>437</v>
       </c>
@@ -6812,7 +6811,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>450</v>
       </c>
@@ -6883,7 +6882,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="38" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>462</v>
       </c>
@@ -6954,7 +6953,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="39" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>472</v>
       </c>
@@ -7171,7 +7170,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>516</v>
       </c>
@@ -7244,7 +7243,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>529</v>
       </c>
@@ -7315,7 +7314,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="44" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>541</v>
       </c>
@@ -7388,7 +7387,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="45" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>552</v>
       </c>
@@ -7463,7 +7462,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="46" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>567</v>
       </c>
@@ -7538,7 +7537,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>580</v>
       </c>
@@ -7609,7 +7608,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>594</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>607</v>
       </c>
@@ -7751,7 +7750,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="50" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>618</v>
       </c>
@@ -7822,7 +7821,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>630</v>
       </c>
@@ -7893,7 +7892,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="52" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>644</v>
       </c>
@@ -7966,7 +7965,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="53" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>658</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="54" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>670</v>
       </c>
@@ -8183,7 +8182,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>696</v>
       </c>
@@ -8254,7 +8253,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="57" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>711</v>
       </c>
@@ -8325,7 +8324,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="58" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>723</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="59" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>737</v>
       </c>
@@ -8469,7 +8468,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="60" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>747</v>
       </c>
@@ -8542,7 +8541,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="61" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>754</v>
       </c>
@@ -8615,7 +8614,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="62" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>762</v>
       </c>
@@ -8686,7 +8685,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="63" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>772</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="64" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>781</v>
       </c>
@@ -8832,7 +8831,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="65" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>788</v>
       </c>
@@ -8976,7 +8975,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="67" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>816</v>
       </c>
@@ -9047,7 +9046,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="68" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>830</v>
       </c>
@@ -9118,7 +9117,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="69" spans="1:33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>838</v>
       </c>
@@ -9261,60 +9260,42 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:AG70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:AG70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="32">
       <filters>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <x14:filter val="Priority 1. Access: Open (CC BY 3.0; data on ManyPrimates GitHub). Suggested home: __merging_behaviour (cognition). Registry/roadmap status at scouting: Registered (species predictors only). Folder ManyPrimates__2022 already registered (species predictors) — add this as a second item in that folder."/>
-            <x14:filter val="Priority 1. Access: Open (PMC3177596). Suggested home: Neuromodulatory innervation (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open (PMC3557031). Suggested home: __merging_cellcounts (regional M1/V1). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open (PMC4424698). Suggested home: __merging_behaviour (hand morphology). Registry/roadmap status at scouting: Not registered — flagged in your roadmap."/>
-            <x14:filter val="Priority 1. Access: Open (PMC5014138). Suggested home: __merging_cellcounts (entorhinal regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open (PMC5845477). Suggested home: __merging_cellcounts (spinal cord). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open (PMC6075024). Suggested home: __merging_cortical_areas (M1 extent and organisation). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open (PNAS). Suggested home: __merging_cellcounts (regional glia–neuron ratio). Registry/roadmap status at scouting: Not registered — relates to your cell-proportions note."/>
-            <x14:filter val="Priority 1. Access: Open copy (publisher PDF via Unpaywall). Suggested home: __merging_cell_morphology (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Open copy (publisher PDF via Unpaywall). Suggested home: New measure class: neuromodulatory innervation (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cell_morphology (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cellcounts (entorhinal regional). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cellcounts (spinal cord). Registry/roadmap status at scouting: Not registered — may match your spinal-cord TODO."/>
-            <x14:filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: CST termination grade (Bortoff &amp; Strick lineage); __merging_cortical_areas. Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Karger). Suggested home: __merging_gyrification. Registry/roadmap status at scouting: Not registered — primary behind the gyrification merge."/>
-            <x14:filter val="Priority 1. Access: Subscription (Oxford). Suggested home: __merging_cellcounts (new term: neurons per column / per mm² surface, by area). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_behaviour (CST axis); regional M1 counts in __merging_cellcounts. Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_behaviour (new term: pyramidal-tract fibre number). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cellcounts (regional M1); __merging_cell_morphology. Registry/roadmap status at scouting: Not registered — flagged in your roadmap."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cellcounts (spinal cord), beside Burish 2010 and Fu 2013. Registry/roadmap status at scouting: Not registered — may match your spinal-cord TODO."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cortical_areas (sensorimotor organisation). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cortical_areas; CST origin (with A01). Registry/roadmap status at scouting: Not registered."/>
-            <x14:filter val="Priority 1. Access: Subscription (Wiley). Suggested home: Neuromodulatory innervation (M1 regional); specimen registry. Registry/roadmap status at scouting: Not registered."/>
-          </mc:Choice>
-          <mc:Fallback>
-            <filter val="Priority 1. Access: Open (PMC3177596). Suggested home: Neuromodulatory innervation (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open (PMC3557031). Suggested home: __merging_cellcounts (regional M1/V1). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open (PMC4424698). Suggested home: __merging_behaviour (hand morphology). Registry/roadmap status at scouting: Not registered — flagged in your roadmap."/>
-            <filter val="Priority 1. Access: Open (PMC5014138). Suggested home: __merging_cellcounts (entorhinal regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open (PMC5845477). Suggested home: __merging_cellcounts (spinal cord). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open (PMC6075024). Suggested home: __merging_cortical_areas (M1 extent and organisation). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open (PNAS). Suggested home: __merging_cellcounts (regional glia–neuron ratio). Registry/roadmap status at scouting: Not registered — relates to your cell-proportions note."/>
-            <filter val="Priority 1. Access: Open copy (publisher PDF via Unpaywall). Suggested home: __merging_cell_morphology (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Open copy (publisher PDF via Unpaywall). Suggested home: New measure class: neuromodulatory innervation (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cell_morphology (M1 regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cellcounts (entorhinal regional). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: __merging_cellcounts (spinal cord). Registry/roadmap status at scouting: Not registered — may match your spinal-cord TODO."/>
-            <filter val="Priority 1. Access: Subscription (Elsevier). Suggested home: CST termination grade (Bortoff &amp; Strick lineage); __merging_cortical_areas. Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Karger). Suggested home: __merging_gyrification. Registry/roadmap status at scouting: Not registered — primary behind the gyrification merge."/>
-            <filter val="Priority 1. Access: Subscription (Oxford). Suggested home: __merging_cellcounts (new term: neurons per column / per mm² surface, by area). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_behaviour (CST axis); regional M1 counts in __merging_cellcounts. Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_behaviour (new term: pyramidal-tract fibre number). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cellcounts (regional M1); __merging_cell_morphology. Registry/roadmap status at scouting: Not registered — flagged in your roadmap."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cellcounts (spinal cord), beside Burish 2010 and Fu 2013. Registry/roadmap status at scouting: Not registered — may match your spinal-cord TODO."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cortical_areas (sensorimotor organisation). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: __merging_cortical_areas; CST origin (with A01). Registry/roadmap status at scouting: Not registered."/>
-            <filter val="Priority 1. Access: Subscription (Wiley). Suggested home: Neuromodulatory innervation (M1 regional); specimen registry. Registry/roadmap status at scouting: Not registered."/>
-          </mc:Fallback>
-        </mc:AlternateContent>
+        <filter val="Priority 2. Access: Open (Ohio J Sci back issues on Internet Archive / OSU). Suggested home: Backbone brain/body mass (within-species samples). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (per-neuron download). Suggested home: __merging_cell_morphology (species × region × cell-type summaries). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC3432265). Suggested home: __merging_cortical_areas (V1 and sensory field sizes). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC3727908). Suggested home: __merging_cellcounts (V1 regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC3918685). Suggested home: __merging_cell_morphology (V1 regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC4034204). Suggested home: __merging_behaviour (cognition). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC4510966). Suggested home: __merging_behaviour (hand morphology). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC8152890). Suggested home: __merging_cellcounts (V1 interneuron classes). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC8463089). Suggested home: __merging_cellcounts / synapse density (V1). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (PMC8734557). Suggested home: New binary trait (adult hippocampal neurogenesis); __merging_volumes (new cetacean values only). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Open (public-domain PDF, NLM). Suggested home: __merging_cerebral_metabolic_rate (regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Postprint (University of Zurich repository). Suggested home: __merging_cellcounts (entorhinal regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Acoustical Society of America). Suggested home: __merging_sensory (percepts). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (APA). Suggested home: __merging_sensory (percepts). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Canadian Science Publishing). Suggested home: __merging_behaviour (dexterity). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Elsevier). Suggested home: __merging_sensory (percepts). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Elsevier). Suggested home: __merging_volumes (hippocampal subdivisions). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Karger). Suggested home: __merging_cellcounts (V1 interneuron classes). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Karger). Suggested home: __merging_sensory (percepts). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Karger). Suggested home: New white-matter block (callosal fibres). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Oxford). Suggested home: __merging_cellcounts (V1 interneuron classes). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Royal Society). Suggested home: __merging_sensory (eye morphology). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Springer); PDF on Japan Monkey Centre site. Suggested home: __merging_behaviour (manipulation repertoire). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Springer). Suggested home: __merging_cell_morphology (M1 and V1 regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Springer). Suggested home: __merging_cell_morphology. Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Springer). Suggested home: __merging_cellcounts (cerebellum). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_cellcounts; __merging_cortical_areas; __merging_volumes. Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_cerebral_metabolic_rate (regional). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_cortical_areas (new term: CST cortex area). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_gyrification. Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_sensory (percepts). Registry/roadmap status at scouting: Not registered."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_weights; spinal-cord block. Registry/roadmap status at scouting: Not registered — on your spinal-cord TODO list."/>
+        <filter val="Priority 2. Access: Subscription (Wiley). Suggested home: __merging_weights; spinal-cord block. Registry/roadmap status at scouting: Not registered."/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -11936,12 +11917,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12200,20 +12183,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07583C61-2424-491A-BB29-A9C32904773A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20E02404-B95A-4B8E-8C82-EE8219052BB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12238,18 +12228,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20E02404-B95A-4B8E-8C82-EE8219052BB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07583C61-2424-491A-BB29-A9C32904773A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>